--- a/PP_Comparison.xlsx
+++ b/PP_Comparison.xlsx
@@ -63,11 +63,11 @@
   </si>
   <si>
     <t>Exp
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>Exp
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>DB
@@ -87,11 +87,11 @@
   </si>
   <si>
     <t>DB
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>DB
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>Match</t>
@@ -115,52 +115,52 @@
     <t>X</t>
   </si>
   <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>AV208-1</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>EM - 208</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIFF</t>
+  </si>
+  <si>
+    <t>UPDATE: VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>AV210-1</t>
+  </si>
+  <si>
+    <t>EM - 210</t>
+  </si>
+  <si>
+    <t>UPDATE: EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>AV212-1</t>
+  </si>
+  <si>
+    <t>EM - 212</t>
+  </si>
+  <si>
     <t>NO</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>AV208-1</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>EM - 208</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>DIFF</t>
-  </si>
-  <si>
-    <t>UPDATE: VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>AV210-1</t>
-  </si>
-  <si>
-    <t>EM - 210</t>
-  </si>
-  <si>
-    <t>UPDATE: EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>AV212-1</t>
-  </si>
-  <si>
-    <t>EM - 212</t>
-  </si>
-  <si>
-    <t>NC</t>
   </si>
   <si>
     <t>AV220-1</t>
